--- a/static/Living-bibliography-template.xlsx
+++ b/static/Living-bibliography-template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mhal9222/Desktop/living-bibliography/static/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D2BC5A-F489-FF49-8AB9-B2D0F9A6ED12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15C47B04-097B-3D4D-AC65-5CE37A75D30F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2460" yWindow="640" windowWidth="46280" windowHeight="27980" activeTab="1" xr2:uid="{62C1BFAF-8520-5D4C-BFE9-88B66F49E369}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Title</t>
   </si>
@@ -70,18 +70,12 @@
     <t>Related source titles</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>A living bibliography</t>
   </si>
   <si>
     <t>Generator</t>
   </si>
   <si>
-    <t>Date added to bibliography</t>
-  </si>
-  <si>
     <t>Latitude</t>
   </si>
   <si>
@@ -106,10 +100,25 @@
     <t>Example</t>
   </si>
   <si>
-    <t>https//www.google.com</t>
-  </si>
-  <si>
     <t>A source</t>
+  </si>
+  <si>
+    <t>Date updated</t>
+  </si>
+  <si>
+    <t>Slug</t>
+  </si>
+  <si>
+    <t>template</t>
+  </si>
+  <si>
+    <t>A narrative section</t>
+  </si>
+  <si>
+    <t>This is a narrative section, it can have as much text content you want contextualising or grouping sources in the bibliography.</t>
+  </si>
+  <si>
+    <t>https://www.google.com</t>
   </si>
 </sst>
 </file>
@@ -534,7 +543,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08788AED-5B1A-3845-92D9-4AC8EBF0A781}">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -543,7 +552,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -551,7 +560,7 @@
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -559,22 +568,38 @@
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B6" t="s">
-        <v>18</v>
+        <v>21</v>
+      </c>
+      <c r="B6" s="1">
+        <v>45566</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
         <v>1</v>
       </c>
     </row>
@@ -585,212 +610,173 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6608C388-4639-4F4E-9326-DC48CED4E1B6}">
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="53.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18.85546875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="42.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="43.7109375" customWidth="1"/>
-    <col min="6" max="6" width="25.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.140625" customWidth="1"/>
-    <col min="8" max="9" width="18.85546875" customWidth="1"/>
-    <col min="10" max="10" width="42.7109375" style="3" customWidth="1"/>
-    <col min="11" max="11" width="25.42578125" customWidth="1"/>
+    <col min="3" max="3" width="42.7109375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="43.7109375" customWidth="1"/>
+    <col min="5" max="5" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="18.85546875" customWidth="1"/>
+    <col min="8" max="8" width="42.7109375" style="3" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="17">
+    <row r="1" spans="1:9" ht="17">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>4</v>
       </c>
+      <c r="D1" s="6" t="s">
+        <v>5</v>
+      </c>
       <c r="E1" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="G1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J1" s="8"/>
-      <c r="K1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" ht="17">
+      <c r="H1" s="8"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" ht="17">
       <c r="A2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1">
-        <v>44338</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G2" s="1">
-        <v>45386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="E2" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="1"/>
-      <c r="K3" s="3"/>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="D3" s="3"/>
+      <c r="E3" s="4"/>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="3"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="1"/>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="1"/>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="D5" s="3"/>
+      <c r="E5" s="4"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="3"/>
-      <c r="C6" s="1"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="1"/>
-      <c r="K6" s="3"/>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="E6" s="2"/>
+      <c r="I6" s="3"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="D7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="3"/>
-      <c r="D8" s="9"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="1"/>
-      <c r="J8" s="9"/>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="C8" s="9"/>
+      <c r="E8" s="2"/>
+      <c r="H8" s="9"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="1"/>
-      <c r="K9" s="3"/>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="D9" s="3"/>
+      <c r="E9" s="2"/>
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="3"/>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:11">
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="D11" s="3"/>
+      <c r="E11" s="4"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="3"/>
-      <c r="C12" s="1"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="1"/>
-      <c r="K12" s="3"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="E12" s="2"/>
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="3"/>
-      <c r="C13" s="1"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="3"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="3"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="1"/>
-      <c r="K15" s="3"/>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="E15" s="2"/>
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="3"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="1:11">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="C18" s="1"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="1"/>
-      <c r="K18" s="3"/>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="C19" s="1"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="1:11">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="E18" s="2"/>
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="1:11">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="1"/>
-      <c r="K21" s="3"/>
-    </row>
-    <row r="22" spans="1:11">
+      <c r="E21" s="2"/>
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="1"/>
-    </row>
-    <row r="23" spans="1:11">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-    </row>
-    <row r="24" spans="1:11">
+      <c r="D23" s="10"/>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="9"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="1"/>
-      <c r="K24" s="3"/>
-    </row>
-    <row r="25" spans="1:11">
+      <c r="E24" s="2"/>
+      <c r="I24" s="3"/>
+    </row>
+    <row r="25" spans="1:9">
       <c r="A25" s="3"/>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:9">
       <c r="A26" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{4E200C61-F3B3-2645-838E-67E015B66196}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -817,6 +803,17 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2" spans="1:3" ht="34">
+      <c r="A2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="3" spans="1:3">
       <c r="B3" s="5"/>
     </row>
